--- a/NECP Scenario/Results/Regional Results/LEMNOS_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/LEMNOS_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.333430238243012E-08</v>
+        <v>4.923135839651733E-08</v>
       </c>
       <c r="C3">
-        <v>1.917790370951866E-08</v>
+        <v>2.83228479513432E-08</v>
       </c>
       <c r="D3">
-        <v>0.03542311479884005</v>
+        <v>0.03542287536292311</v>
       </c>
       <c r="E3">
-        <v>0.3532199021902767</v>
+        <v>0.3918580364066416</v>
       </c>
       <c r="F3">
-        <v>0.4954509438400822</v>
+        <v>0.5505114196519902</v>
       </c>
       <c r="G3">
-        <v>0.6437156112006764</v>
+        <v>0.6575093540503663</v>
       </c>
       <c r="H3">
-        <v>0.5965935714676518</v>
+        <v>0.6519758507790027</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.833415702728745E-08</v>
+        <v>4.184665463883977E-08</v>
       </c>
       <c r="C4">
-        <v>1.63012181553127E-08</v>
+        <v>2.407442076044178E-08</v>
       </c>
       <c r="D4">
-        <v>0.03010964757903519</v>
+        <v>0.03010944405848211</v>
       </c>
       <c r="E4">
-        <v>0.3002369168626695</v>
+        <v>0.3330793309454484</v>
       </c>
       <c r="F4">
-        <v>0.4211333022630797</v>
+        <v>0.4679347067040029</v>
       </c>
       <c r="G4">
-        <v>0.5471582695189151</v>
+        <v>0.5588829509427081</v>
       </c>
       <c r="H4">
-        <v>0.5071045357475847</v>
+        <v>0.5541794731620534</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.05476367907091099</v>
+        <v>0.05476368019703463</v>
       </c>
       <c r="C14">
-        <v>0.06229076790391128</v>
+        <v>0.06229076839802231</v>
       </c>
       <c r="D14">
-        <v>0.06872749617659143</v>
+        <v>0.06872748686645526</v>
       </c>
       <c r="E14">
-        <v>0.06552599683314343</v>
+        <v>0.06533449100838881</v>
       </c>
       <c r="F14">
-        <v>0.07799575197082406</v>
+        <v>0.07641117875111468</v>
       </c>
       <c r="G14">
-        <v>0.09487464767300879</v>
+        <v>0.09487468094970831</v>
       </c>
       <c r="H14">
-        <v>0.1252781152949964</v>
+        <v>0.1252783171658754</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.1547931276655634</v>
+        <v>0.1547931520058388</v>
       </c>
       <c r="C28">
-        <v>0.1818291802569522</v>
+        <v>0.1818291920385362</v>
       </c>
       <c r="D28">
-        <v>0.02394117352739244</v>
+        <v>0.0239413037859879</v>
       </c>
       <c r="E28">
-        <v>3.969305580409105E-08</v>
+        <v>5.883064425339072E-08</v>
       </c>
       <c r="F28">
-        <v>4.065575404318804E-08</v>
+        <v>6.01188586194641E-08</v>
       </c>
       <c r="G28">
-        <v>4.573930739823394E-08</v>
+        <v>6.767277972238914E-08</v>
       </c>
       <c r="H28">
-        <v>2.486527150663703E-07</v>
+        <v>3.678355176404804E-07</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.04397532034967492</v>
+        <v>0.04397532725982601</v>
       </c>
       <c r="C29">
-        <v>0.05165601711329478</v>
+        <v>0.05165602045787487</v>
       </c>
       <c r="D29">
-        <v>0.006801469744514453</v>
+        <v>0.006801506746179843</v>
       </c>
       <c r="E29">
-        <v>1.126528220149848E-08</v>
+        <v>1.669678022777495E-08</v>
       </c>
       <c r="F29">
-        <v>1.153353011043767E-08</v>
+        <v>1.705500629757849E-08</v>
       </c>
       <c r="G29">
-        <v>1.29700095674153E-08</v>
+        <v>1.918962293620518E-08</v>
       </c>
       <c r="H29">
-        <v>7.049372861014466E-08</v>
+        <v>1.042828528581481E-07</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.04608456678067342</v>
+        <v>0.04608416798051916</v>
       </c>
       <c r="E30">
-        <v>0.1887060198655639</v>
+        <v>0.1996058459215032</v>
       </c>
       <c r="F30">
-        <v>0.2036173010758104</v>
+        <v>0.2033111414412038</v>
       </c>
       <c r="G30">
-        <v>0.2036165534177302</v>
+        <v>0.2031991782616559</v>
       </c>
       <c r="H30">
-        <v>0.2036060491158567</v>
+        <v>0.2031945311651291</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.002876015690380367</v>
+        <v>0.002876014515047006</v>
       </c>
       <c r="C31">
-        <v>0.002876017086049619</v>
+        <v>0.002876016574987369</v>
       </c>
       <c r="D31">
-        <v>0.002276271234930822</v>
+        <v>0.002275235737041411</v>
       </c>
       <c r="E31">
-        <v>0.00287487668402554</v>
+        <v>0.002868933503961563</v>
       </c>
       <c r="F31">
-        <v>0.002874355400066762</v>
+        <v>0.002857349082863685</v>
       </c>
       <c r="G31">
-        <v>0.002873694136909622</v>
+        <v>0.002843960955791918</v>
       </c>
       <c r="H31">
-        <v>0.00286455481386631</v>
+        <v>0.002839957599853604</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>4.589873977363178E-08</v>
+        <v>6.78478271303466E-08</v>
       </c>
       <c r="E32">
-        <v>0.01709981825081472</v>
+        <v>0.01729948050631075</v>
       </c>
       <c r="F32">
-        <v>0.02259137317927796</v>
+        <v>0.02424267374736492</v>
       </c>
       <c r="G32">
-        <v>0.0247215290558578</v>
+        <v>0.02472154088106906</v>
       </c>
       <c r="H32">
-        <v>0.02490424539886062</v>
+        <v>0.02490413437901794</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.003012969074294681</v>
+        <v>0.003012967964602152</v>
       </c>
       <c r="C33">
-        <v>0.003012970385315682</v>
+        <v>0.003012969899813126</v>
       </c>
       <c r="D33">
-        <v>0.003012944468564855</v>
+        <v>0.003012931842295873</v>
       </c>
       <c r="E33">
-        <v>0.002924422386273482</v>
+        <v>0.002916265974189012</v>
       </c>
       <c r="F33">
-        <v>0.002868976277566792</v>
+        <v>0.002802248956601382</v>
       </c>
       <c r="G33">
-        <v>0.002936106275269024</v>
+        <v>0.00293606121363471</v>
       </c>
       <c r="H33">
-        <v>0.003012251297229773</v>
+        <v>0.003012160690323451</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.01447782732050415</v>
+        <v>0.01447556319617695</v>
       </c>
       <c r="E36">
-        <v>1.008143987927297</v>
+        <v>0.9587637924881078</v>
       </c>
       <c r="F36">
-        <v>1.114686638360682</v>
+        <v>1.08736025306541</v>
       </c>
       <c r="G36">
-        <v>1.133955873142819</v>
+        <v>1.094313069378219</v>
       </c>
       <c r="H36">
-        <v>1.141922489028182</v>
+        <v>1.108479647756666</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.009029974168976312</v>
+        <v>0.009029971984281366</v>
       </c>
       <c r="C37">
-        <v>0.009029976760590535</v>
+        <v>0.009029975811605258</v>
       </c>
       <c r="D37">
-        <v>0.005803430305176938</v>
+        <v>0.005807046323078192</v>
       </c>
       <c r="E37">
-        <v>0.007039722925284361</v>
+        <v>0.00702039215979748</v>
       </c>
       <c r="F37">
-        <v>0.007100040283873754</v>
+        <v>0.006947800601043018</v>
       </c>
       <c r="G37">
-        <v>0.007195288259508758</v>
+        <v>0.007082126127654006</v>
       </c>
       <c r="H37">
-        <v>0.007249908640643509</v>
+        <v>0.007061407482402292</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>9.373799687010769E-09</v>
+        <v>1.384352054673017E-08</v>
       </c>
       <c r="C38">
-        <v>4.075495210412709E-09</v>
+        <v>6.021045285867518E-09</v>
       </c>
       <c r="D38">
-        <v>0.01538089483087271</v>
+        <v>0.01538087064795151</v>
       </c>
       <c r="E38">
-        <v>0.171056235723345</v>
+        <v>0.176914774956789</v>
       </c>
       <c r="F38">
-        <v>0.2182678038575218</v>
+        <v>0.2462489100566985</v>
       </c>
       <c r="G38">
-        <v>0.1986431669662457</v>
+        <v>0.2386744562484069</v>
       </c>
       <c r="H38">
-        <v>0.1903827183939732</v>
+        <v>0.2242785610161941</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.333430238243012E-08</v>
+        <v>4.923135839651733E-08</v>
       </c>
       <c r="C40">
-        <v>1.917790370951866E-08</v>
+        <v>2.83228479513432E-08</v>
       </c>
       <c r="D40">
-        <v>0.03542311479884005</v>
+        <v>0.03542287536292311</v>
       </c>
       <c r="E40">
-        <v>0.3532199021902767</v>
+        <v>0.3918580364066416</v>
       </c>
       <c r="F40">
-        <v>0.4954509438400822</v>
+        <v>0.5505114196519902</v>
       </c>
       <c r="G40">
-        <v>0.6437156112006764</v>
+        <v>0.6575093540503663</v>
       </c>
       <c r="H40">
-        <v>0.5965935714676518</v>
+        <v>0.6519758507790027</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>2.833415702728745E-08</v>
+        <v>4.184665463883977E-08</v>
       </c>
       <c r="C41">
-        <v>1.63012181553127E-08</v>
+        <v>2.407442076044178E-08</v>
       </c>
       <c r="D41">
-        <v>0.03010964757903519</v>
+        <v>0.03010944405848211</v>
       </c>
       <c r="E41">
-        <v>0.3002369168626695</v>
+        <v>0.3330793309454484</v>
       </c>
       <c r="F41">
-        <v>0.4211333022630797</v>
+        <v>0.4679347067040029</v>
       </c>
       <c r="G41">
-        <v>0.5471582695189151</v>
+        <v>0.5588829509427081</v>
       </c>
       <c r="H41">
-        <v>0.5071045357475847</v>
+        <v>0.5541794731620534</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.000145355142672E-09</v>
+        <v>-7.384703757677567E-09</v>
       </c>
       <c r="C42">
-        <v>-2.876685554205957E-09</v>
+        <v>-4.248427190901417E-09</v>
       </c>
       <c r="D42">
-        <v>-0.005313467219804861</v>
+        <v>-0.005313431304441001</v>
       </c>
       <c r="E42">
-        <v>-0.0529829853276072</v>
+        <v>-0.05877870546119318</v>
       </c>
       <c r="F42">
-        <v>-0.07431764157700249</v>
+        <v>-0.0825767129479873</v>
       </c>
       <c r="G42">
-        <v>-0.09655734168176133</v>
+        <v>-0.09862640310765813</v>
       </c>
       <c r="H42">
-        <v>-0.08948903572006706</v>
+        <v>-0.09779637761694926</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1612,16 +1612,16 @@
         <v>-0</v>
       </c>
       <c r="E43">
-        <v>-1.086918371226027</v>
+        <v>-1.042812427283304</v>
       </c>
       <c r="F43">
-        <v>-1.174373203008689</v>
+        <v>-1.13992925765023</v>
       </c>
       <c r="G43">
-        <v>-1.154273215187839</v>
+        <v>-1.112001051752171</v>
       </c>
       <c r="H43">
-        <v>-1.138319224333923</v>
+        <v>-1.09594425239664</v>
       </c>
     </row>
     <row r="44" spans="1:8">
